--- a/output/2026-10-03_07_Malesia_Perak_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-03_07_Malesia_Perak_Impiantistica_aspirazione_industriale.xlsx
@@ -464,7 +464,6 @@
           <t>Kee Ming Electrical Sdn Bhd (Kee Ming Group Berhad)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Ipoh, Perak</t>
@@ -475,8 +474,6 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Verificato via WebSearch (hiredly, jobstreet, NST, The Star, isaham.my). Societa' di ingegneria M&amp;E con sede a Falim, Ipoh, Perak (No 19, 19A &amp; 19B, Jalan Pusat Perniagaan Falim 3, 30200 Ipoh). Contractor CIDB Grade 7, certificato ISO 9001:2015, quotata su Bursa Malaysia ACE Market (Feb 2026) come Kee Ming Group Berhad. Attiva in ACMV/HVAC (ventilazione meccanica industriale), clean room systems, fire protection, EPCC. Integratore di impianti di ventilazione, non specializzato esclusivamente in dust collection/aspirazione: valutare la pertinenza esatta. Nessun sito web ufficiale ne' telefono/email diretti confermati (numero originale incompleto, dominio keeming.com.my non raggiungibile/non confermato) - lasciati vuoti per non inventare dati.</t>
@@ -521,7 +518,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Verificato via WebSearch (pagine ufficiali lapasar.com/b2b-procurement-ipoh, lapasar.com/mro-industrial-supplies-supplier-ipoh, mall.lapasar.com/category/industrial-equipment/dust-extractors). Marketplace B2B/distributore logistico multi-categoria (MRO, safety, industrial equipment) con categoria dedicata 'Dust Extractors'. Sede legale a Klang, Selangor; copertura confermata su Ipoh e Kinta Valley (Chemor, Kanthan, Tasek Industrial Estate) tramite flotta propria e consegna diretta da magazzino Klang Valley. Non e' uno specialista di impiantistica di aspirazione industriale ma un marketplace generalista che include la categoria: valutare pertinenza rispetto a distributori specializzati.</t>
+          <t>Verificato via WebSearch (pagine ufficiali lapasar.com/b2b-procurement-ipoh, lapasar.com/mro-industrial-supplies-supplier-ipoh, mall.lapasar.com/category/industrial-equipment/dust-extractors). Marketplace B2B/distributore logistico multi-categoria (MRO, safety, industrial equipment) con categoria dedicata 'Dust Extractors'. Sede legale a Klang, Selangor; copertura confermata su Ipoh e Kinta Valley (Chemor, Kanthan, Tasek Industrial Estate) tramite flotta propria e consegna diretta da magazzino Klang Valley. Non e' uno specialista di impiantistica di aspirazione industriale ma un marketplace generalista che include la categoria: valutare pertinenza rispetto a distributori specializzati. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
